--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-vaccination-document.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-vaccination-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$139</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5150" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5114" uniqueCount="659">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,9 +84,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>L'entrée Vaccination est une entrée de type 'substanceAdministration' pour décrire l'administration d'un vaccin. 
- - Elle permet également de décrire pourquoi un vaccin n'a pas été réalisé.
- - Cette entrée hérite de la structuration, des contraintes et des vocabulaires de l'entrée Traitement (1.3.6.1.4.1.19376.1.5.3.1.4.7) sauf mentions précisées ci-après.</t>
+    <t>FrVaccinationDocument permet de décrire l'administration d'un vaccin. 
+ - Il permet également de décrire pourquoi un vaccin n'a pas été réalisé.
+ - Ce profil hérite de la structuration, des contraintes et des vocabulaires définis dans le profil FrMedicationAdministrationDocument sauf mentions précisées ci-après.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -470,7 +470,7 @@
 </t>
   </si>
   <si>
-    <t>Fr Vaccination Type</t>
+    <t>Extension - Fr Vaccination Type</t>
   </si>
   <si>
     <t>Extension représentant le type de vaccination (ex: INITIMMUNIZ, BOOSTER, IMMUNIZ), équivalent au code de l'entrée CDA FR-Vaccination.</t>
@@ -506,10 +506,10 @@
 </t>
   </si>
   <si>
-    <t>Fr Prescription</t>
-  </si>
-  <si>
-    <t>Instructions de prescription associées à l'administration du produit de santé.</t>
+    <t>Extension - Fr Prescription</t>
+  </si>
+  <si>
+    <t>Extension permettant d’indiquer les instructions de prescription associées à l'administration du produit de santé.</t>
   </si>
   <si>
     <t>Immunization.extension:doseAntigene</t>
@@ -522,7 +522,7 @@
 </t>
   </si>
   <si>
-    <t>Fr Dose Antigene</t>
+    <t>Extension - Fr Dose Antigene</t>
   </si>
   <si>
     <t>Extension complexe pour représenter un consommable (FrMedication) et une doseQuantity dans Immunization.</t>
@@ -770,35 +770,22 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.extension:translation.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>Immunization.vaccineCode.extension:translation.value[x]:valueCodeableConcept.id</t>
+    <t>Immunization.vaccineCode.extension:translation.value[x].id</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.extension.value[x].id</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.extension:translation.value[x]:valueCodeableConcept.extension</t>
+    <t>Immunization.vaccineCode.extension:translation.value[x].extension</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.extension.value[x].extension</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.extension:translation.value[x]:valueCodeableConcept.coding</t>
+    <t>Immunization.vaccineCode.extension:translation.value[x].coding</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.extension.value[x].coding</t>
@@ -829,19 +816,19 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.extension:translation.value[x]:valueCodeableConcept.coding.id</t>
+    <t>Immunization.vaccineCode.extension:translation.value[x].coding.id</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.extension.value[x].coding.id</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.extension:translation.value[x]:valueCodeableConcept.coding.extension</t>
+    <t>Immunization.vaccineCode.extension:translation.value[x].coding.extension</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.extension.value[x].coding.extension</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.extension:translation.value[x]:valueCodeableConcept.coding.system</t>
+    <t>Immunization.vaccineCode.extension:translation.value[x].coding.system</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.extension.value[x].coding.system</t>
@@ -871,7 +858,7 @@
     <t>./codeSystem</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.extension:translation.value[x]:valueCodeableConcept.coding.version</t>
+    <t>Immunization.vaccineCode.extension:translation.value[x].coding.version</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.extension.value[x].coding.version</t>
@@ -895,7 +882,7 @@
     <t>./codeSystemVersion</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.extension:translation.value[x]:valueCodeableConcept.coding.code</t>
+    <t>Immunization.vaccineCode.extension:translation.value[x].coding.code</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.extension.value[x].coding.code</t>
@@ -919,7 +906,7 @@
     <t>./code</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.extension:translation.value[x]:valueCodeableConcept.coding.display</t>
+    <t>Immunization.vaccineCode.extension:translation.value[x].coding.display</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.extension.value[x].coding.display</t>
@@ -943,7 +930,7 @@
     <t>CV.displayName</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.extension:translation.value[x]:valueCodeableConcept.coding.userSelected</t>
+    <t>Immunization.vaccineCode.extension:translation.value[x].coding.userSelected</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.extension.value[x].coding.userSelected</t>
@@ -974,7 +961,7 @@
     <t>CD.codingRationale</t>
   </si>
   <si>
-    <t>Immunization.vaccineCode.extension:translation.value[x]:valueCodeableConcept.text</t>
+    <t>Immunization.vaccineCode.extension:translation.value[x].text</t>
   </si>
   <si>
     <t>Immunization.vaccineCode.extension.value[x].text</t>
@@ -1751,7 +1738,7 @@
     <t>Immunization.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-condition)
 </t>
   </si>
   <si>
@@ -2035,6 +2022,13 @@
   </si>
   <si>
     <t>The use of an integer is preferred if known. A string should only be used in cases where an integer is not available (such as when documenting a recurring booster dose).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
   </si>
   <si>
     <t>Immunization.protocolApplied.doseNumber[x]:doseNumberPositiveInt</t>
@@ -2373,10 +2367,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO140"/>
+  <dimension ref="A1:AO139"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="81.51953125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="65.734375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="53.828125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="19.14453125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
@@ -5289,17 +5283,19 @@
         <v>78</v>
       </c>
       <c r="AB25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AC25" s="2"/>
-      <c r="AD25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
@@ -5331,20 +5327,18 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="C26" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>89</v>
@@ -5359,13 +5353,13 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>239</v>
+        <v>211</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>240</v>
+        <v>212</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5416,7 +5410,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>243</v>
+        <v>213</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5428,7 +5422,7 @@
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
@@ -5437,7 +5431,7 @@
         <v>78</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>132</v>
+        <v>214</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>78</v>
@@ -5448,21 +5442,21 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>78</v>
+        <v>164</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>78</v>
@@ -5474,15 +5468,17 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
@@ -5519,31 +5515,31 @@
         <v>78</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>78</v>
@@ -5563,14 +5559,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>164</v>
+        <v>78</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5586,21 +5582,23 @@
         <v>78</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>135</v>
+        <v>248</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>216</v>
+        <v>249</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>217</v>
+        <v>250</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>78</v>
       </c>
@@ -5636,19 +5634,19 @@
         <v>78</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>219</v>
+        <v>253</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -5660,16 +5658,16 @@
         <v>78</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>78</v>
+        <v>254</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>214</v>
+        <v>255</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -5680,10 +5678,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5694,7 +5692,7 @@
         <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>78</v>
@@ -5703,23 +5701,19 @@
         <v>78</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>252</v>
+        <v>210</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>253</v>
+        <v>211</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>256</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>78</v>
       </c>
@@ -5767,28 +5761,28 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>257</v>
+        <v>213</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>258</v>
+        <v>78</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>259</v>
+        <v>214</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -5799,21 +5793,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>78</v>
+        <v>164</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>78</v>
@@ -5825,15 +5819,17 @@
         <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>78</v>
@@ -5870,31 +5866,31 @@
         <v>78</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>78</v>
@@ -5914,21 +5910,21 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>164</v>
+        <v>78</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>78</v>
@@ -5937,21 +5933,23 @@
         <v>78</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>217</v>
+        <v>263</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>78</v>
       </c>
@@ -5975,52 +5973,50 @@
         <v>78</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y31" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>78</v>
+        <v>266</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>219</v>
+        <v>267</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>78</v>
+        <v>268</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>214</v>
+        <v>269</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>78</v>
@@ -6031,10 +6027,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6057,20 +6053,18 @@
         <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>103</v>
+        <v>210</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>269</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>78</v>
       </c>
@@ -6094,11 +6088,13 @@
         <v>78</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y32" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z32" t="s" s="2">
-        <v>270</v>
+        <v>78</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>78</v>
@@ -6116,7 +6112,7 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -6134,10 +6130,10 @@
         <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>78</v>
@@ -6148,10 +6144,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6174,18 +6170,18 @@
         <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>210</v>
+        <v>109</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>78</v>
       </c>
@@ -6233,7 +6229,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -6251,10 +6247,10 @@
         <v>78</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>78</v>
@@ -6265,10 +6261,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6291,17 +6287,17 @@
         <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>109</v>
+        <v>210</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
@@ -6350,7 +6346,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -6368,10 +6364,10 @@
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>78</v>
@@ -6382,10 +6378,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6408,17 +6404,19 @@
         <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>210</v>
+        <v>296</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>299</v>
+      </c>
       <c r="O35" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
@@ -6467,7 +6465,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -6485,10 +6483,10 @@
         <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>78</v>
@@ -6499,10 +6497,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6525,19 +6523,19 @@
         <v>90</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>300</v>
+        <v>210</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6586,7 +6584,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -6604,10 +6602,10 @@
         <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>78</v>
@@ -6618,10 +6616,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6632,7 +6630,7 @@
         <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>78</v>
@@ -6644,19 +6642,19 @@
         <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>210</v>
+        <v>248</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>310</v>
+        <v>249</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>311</v>
+        <v>250</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>312</v>
+        <v>251</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>313</v>
+        <v>252</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -6705,13 +6703,13 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>314</v>
+        <v>253</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>78</v>
@@ -6723,10 +6721,10 @@
         <v>78</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>315</v>
+        <v>254</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>316</v>
+        <v>255</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>78</v>
@@ -6737,10 +6735,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6751,7 +6749,7 @@
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>78</v>
@@ -6763,19 +6761,19 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>252</v>
+        <v>210</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>253</v>
+        <v>306</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>254</v>
+        <v>307</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>255</v>
+        <v>308</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>256</v>
+        <v>309</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -6824,13 +6822,13 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>257</v>
+        <v>310</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>78</v>
@@ -6842,10 +6840,10 @@
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>258</v>
+        <v>311</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>259</v>
+        <v>312</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>78</v>
@@ -6856,10 +6854,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6867,7 +6865,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>89</v>
@@ -6882,20 +6880,16 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>210</v>
+        <v>316</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>78</v>
       </c>
@@ -6943,10 +6937,10 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>89</v>
@@ -6958,16 +6952,16 @@
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>78</v>
+        <v>319</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>78</v>
+        <v>322</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>78</v>
@@ -6975,10 +6969,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6986,7 +6980,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>89</v>
@@ -6998,16 +6992,16 @@
         <v>78</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7058,10 +7052,10 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>89</v>
@@ -7073,16 +7067,16 @@
         <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>78</v>
@@ -7090,10 +7084,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7101,30 +7095,32 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>334</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>78</v>
@@ -7173,10 +7169,10 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>89</v>
@@ -7188,27 +7184,27 @@
         <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>78</v>
+        <v>340</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7216,32 +7212,30 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>336</v>
+        <v>210</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>339</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -7290,10 +7284,10 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>335</v>
+        <v>213</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>89</v>
@@ -7302,30 +7296,30 @@
         <v>78</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>340</v>
+        <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>341</v>
+        <v>78</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>342</v>
+        <v>78</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>343</v>
+        <v>78</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>344</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7336,7 +7330,7 @@
         <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>78</v>
@@ -7348,13 +7342,13 @@
         <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>346</v>
+        <v>229</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>347</v>
+        <v>137</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7393,31 +7387,29 @@
         <v>78</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>78</v>
@@ -7437,12 +7429,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>78</v>
       </c>
@@ -7451,7 +7445,7 @@
         <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>78</v>
@@ -7463,13 +7457,13 @@
         <v>78</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>135</v>
+        <v>347</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>229</v>
+        <v>348</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>137</v>
+        <v>349</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7508,14 +7502,16 @@
         <v>78</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AC44" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>219</v>
@@ -7539,7 +7535,7 @@
         <v>78</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>78</v>
+        <v>350</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>78</v>
@@ -7550,14 +7546,12 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>78</v>
       </c>
@@ -7578,7 +7572,7 @@
         <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="L45" t="s" s="2">
         <v>352</v>
@@ -7635,19 +7629,19 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>219</v>
+        <v>354</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>78</v>
@@ -7656,7 +7650,7 @@
         <v>78</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>354</v>
+        <v>78</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>78</v>
@@ -7693,7 +7687,7 @@
         <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="L46" t="s" s="2">
         <v>356</v>
@@ -7750,31 +7744,31 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="AG46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AN46" t="s" s="2">
-        <v>78</v>
+        <v>359</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>78</v>
@@ -7782,10 +7776,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7805,18 +7799,20 @@
         <v>78</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>336</v>
+        <v>296</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>78</v>
@@ -7865,7 +7861,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7883,13 +7879,13 @@
         <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>78</v>
+        <v>364</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>78</v>
@@ -7897,10 +7893,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7920,19 +7916,19 @@
         <v>78</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>300</v>
+        <v>190</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7958,13 +7954,13 @@
         <v>78</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>78</v>
+        <v>371</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>78</v>
+        <v>372</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>78</v>
@@ -7982,7 +7978,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -8000,13 +7996,13 @@
         <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>78</v>
@@ -8014,10 +8010,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8040,17 +8036,15 @@
         <v>78</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>190</v>
+        <v>375</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>374</v>
-      </c>
+        <v>377</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -8075,13 +8069,13 @@
         <v>78</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>375</v>
+        <v>78</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>376</v>
+        <v>78</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>78</v>
@@ -8099,7 +8093,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8114,16 +8108,16 @@
         <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>78</v>
+        <v>378</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>78</v>
@@ -8131,10 +8125,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8157,13 +8151,13 @@
         <v>78</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8214,7 +8208,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8229,27 +8223,27 @@
         <v>101</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>382</v>
+        <v>78</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>385</v>
+        <v>78</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>78</v>
+        <v>388</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8263,7 +8257,7 @@
         <v>89</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>78</v>
@@ -8272,13 +8266,13 @@
         <v>78</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>387</v>
+        <v>210</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8329,7 +8323,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8347,24 +8341,24 @@
         <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8387,13 +8381,13 @@
         <v>78</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>210</v>
+        <v>396</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8444,7 +8438,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -8462,24 +8456,24 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>398</v>
+        <v>78</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8502,13 +8496,13 @@
         <v>78</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>400</v>
+        <v>190</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8535,13 +8529,11 @@
         <v>78</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>78</v>
+        <v>404</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>78</v>
@@ -8559,7 +8551,7 @@
         <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>79</v>
@@ -8577,24 +8569,24 @@
         <v>78</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>78</v>
+        <v>407</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8620,10 +8612,10 @@
         <v>190</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8654,25 +8646,25 @@
       </c>
       <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF54" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8690,24 +8682,24 @@
         <v>78</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8730,13 +8722,13 @@
         <v>78</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>190</v>
+        <v>416</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8763,29 +8755,31 @@
         <v>78</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y55" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8803,24 +8797,24 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>418</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8831,7 +8825,7 @@
         <v>79</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>90</v>
@@ -8840,16 +8834,16 @@
         <v>78</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8900,13 +8894,13 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>78</v>
@@ -8915,13 +8909,13 @@
         <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>78</v>
+        <v>425</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>78</v>
@@ -8932,10 +8926,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8946,25 +8940,25 @@
         <v>79</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>426</v>
+        <v>210</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>427</v>
+        <v>211</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>428</v>
+        <v>212</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9015,28 +9009,28 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>425</v>
+        <v>213</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>429</v>
+        <v>78</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>430</v>
+        <v>78</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>431</v>
+        <v>214</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>78</v>
@@ -9047,21 +9041,21 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>78</v>
+        <v>164</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>78</v>
@@ -9073,15 +9067,17 @@
         <v>78</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -9130,19 +9126,19 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>78</v>
@@ -9162,14 +9158,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>164</v>
+        <v>431</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -9182,24 +9178,26 @@
         <v>78</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K59" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>216</v>
+        <v>432</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>217</v>
+        <v>433</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="O59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>78</v>
       </c>
@@ -9247,7 +9245,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>219</v>
+        <v>434</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9268,7 +9266,7 @@
         <v>78</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>214</v>
+        <v>132</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -9279,33 +9277,33 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>435</v>
+        <v>78</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J60" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>135</v>
+        <v>190</v>
       </c>
       <c r="L60" t="s" s="2">
         <v>436</v>
@@ -9313,12 +9311,8 @@
       <c r="M60" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="N60" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>168</v>
-      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>78</v>
       </c>
@@ -9342,13 +9336,13 @@
         <v>78</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>78</v>
+        <v>438</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>78</v>
+        <v>439</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>78</v>
+        <v>440</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>78</v>
@@ -9366,28 +9360,28 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>78</v>
+        <v>441</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>132</v>
+        <v>442</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -9398,10 +9392,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9409,7 +9403,7 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G61" t="s" s="2">
         <v>89</v>
@@ -9424,15 +9418,17 @@
         <v>90</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>190</v>
+        <v>444</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>446</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>447</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -9457,34 +9453,34 @@
         <v>78</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>442</v>
+        <v>78</v>
       </c>
       <c r="Y61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF61" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="Z61" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>439</v>
-      </c>
       <c r="AG61" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH61" t="s" s="2">
         <v>89</v>
@@ -9496,16 +9492,16 @@
         <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>78</v>
+        <v>450</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>78</v>
@@ -9513,10 +9509,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9524,7 +9520,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>89</v>
@@ -9536,20 +9532,18 @@
         <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>448</v>
+        <v>210</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>449</v>
+        <v>211</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>451</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>78</v>
@@ -9598,10 +9592,10 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>447</v>
+        <v>213</v>
       </c>
       <c r="AG62" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
         <v>89</v>
@@ -9610,19 +9604,19 @@
         <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>452</v>
+        <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>453</v>
+        <v>214</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>454</v>
+        <v>78</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>78</v>
@@ -9630,10 +9624,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9641,10 +9635,10 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>78</v>
@@ -9656,13 +9650,13 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>212</v>
+        <v>137</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9701,31 +9695,31 @@
         <v>78</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>78</v>
@@ -9734,7 +9728,7 @@
         <v>78</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>214</v>
+        <v>78</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -9745,12 +9739,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="C64" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="C64" t="s" s="2">
+        <v>454</v>
+      </c>
       <c r="D64" t="s" s="2">
         <v>78</v>
       </c>
@@ -9759,7 +9755,7 @@
         <v>89</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>78</v>
@@ -9771,13 +9767,13 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>135</v>
+        <v>455</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>229</v>
+        <v>456</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>137</v>
+        <v>457</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9816,16 +9812,16 @@
         <v>78</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
         <v>219</v>
@@ -9860,20 +9856,18 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>89</v>
@@ -9888,13 +9882,13 @@
         <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>459</v>
+        <v>210</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>460</v>
+        <v>211</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>461</v>
+        <v>212</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9945,19 +9939,19 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>78</v>
@@ -9966,7 +9960,7 @@
         <v>78</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>78</v>
+        <v>214</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>78</v>
@@ -9977,10 +9971,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9988,10 +9982,10 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>78</v>
@@ -10003,13 +9997,13 @@
         <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>212</v>
+        <v>137</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10048,31 +10042,31 @@
         <v>78</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
@@ -10081,7 +10075,7 @@
         <v>78</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>214</v>
+        <v>78</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>78</v>
@@ -10092,21 +10086,23 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C67" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="D67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>78</v>
@@ -10163,16 +10159,16 @@
         <v>78</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
         <v>219</v>
@@ -10207,20 +10203,18 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="C68" t="s" s="2">
-        <v>467</v>
-      </c>
+      <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>89</v>
@@ -10235,13 +10229,13 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>135</v>
+        <v>210</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>137</v>
+        <v>212</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10292,19 +10286,19 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>78</v>
@@ -10313,7 +10307,7 @@
         <v>78</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>78</v>
+        <v>214</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>78</v>
@@ -10324,10 +10318,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10338,7 +10332,7 @@
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>78</v>
@@ -10350,13 +10344,13 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>212</v>
+        <v>137</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10395,31 +10389,31 @@
         <v>78</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>78</v>
@@ -10428,7 +10422,7 @@
         <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>214</v>
+        <v>78</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>78</v>
@@ -10439,10 +10433,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10450,10 +10444,10 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>78</v>
@@ -10465,22 +10459,24 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>78</v>
+        <v>463</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>78</v>
@@ -10510,31 +10506,31 @@
         <v>78</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>78</v>
@@ -10543,7 +10539,7 @@
         <v>78</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>78</v>
@@ -10554,10 +10550,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10565,7 +10561,7 @@
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G71" t="s" s="2">
         <v>89</v>
@@ -10580,24 +10576,22 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q71" s="2"/>
       <c r="R71" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="S71" t="s" s="2">
         <v>78</v>
@@ -10615,13 +10609,11 @@
         <v>78</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>78</v>
+        <v>473</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
@@ -10639,10 +10631,10 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="AG71" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH71" t="s" s="2">
         <v>89</v>
@@ -10651,7 +10643,7 @@
         <v>78</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>78</v>
@@ -10674,9 +10666,11 @@
         <v>474</v>
       </c>
       <c r="B72" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="C72" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>78</v>
       </c>
@@ -10697,13 +10691,13 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>239</v>
+        <v>476</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>240</v>
+        <v>137</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10712,7 +10706,7 @@
       </c>
       <c r="Q72" s="2"/>
       <c r="R72" t="s" s="2">
-        <v>476</v>
+        <v>78</v>
       </c>
       <c r="S72" t="s" s="2">
         <v>78</v>
@@ -10730,11 +10724,13 @@
         <v>78</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y72" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z72" t="s" s="2">
-        <v>477</v>
+        <v>78</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>78</v>
@@ -10752,19 +10748,19 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>78</v>
@@ -10773,7 +10769,7 @@
         <v>78</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -10784,14 +10780,12 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="C73" t="s" s="2">
-        <v>479</v>
-      </c>
+      <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>78</v>
       </c>
@@ -10812,13 +10806,13 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>135</v>
+        <v>210</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>480</v>
+        <v>211</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>137</v>
+        <v>212</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10869,19 +10863,19 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>78</v>
@@ -10890,7 +10884,7 @@
         <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>78</v>
+        <v>214</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>78</v>
@@ -10901,10 +10895,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10915,7 +10909,7 @@
         <v>79</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>78</v>
@@ -10927,13 +10921,13 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>212</v>
+        <v>137</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10972,31 +10966,31 @@
         <v>78</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>78</v>
@@ -11005,7 +10999,7 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>214</v>
+        <v>78</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>78</v>
@@ -11016,10 +11010,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11027,10 +11021,10 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>78</v>
@@ -11042,22 +11036,24 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>78</v>
+        <v>475</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>78</v>
@@ -11087,31 +11083,31 @@
         <v>78</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="AG75" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>78</v>
@@ -11120,7 +11116,7 @@
         <v>78</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
@@ -11131,10 +11127,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11142,7 +11138,7 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>89</v>
@@ -11157,24 +11153,22 @@
         <v>78</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>479</v>
+        <v>78</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>78</v>
@@ -11216,10 +11210,10 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="AG76" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH76" t="s" s="2">
         <v>89</v>
@@ -11228,7 +11222,7 @@
         <v>78</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>78</v>
@@ -11248,18 +11242,20 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C77" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>482</v>
+      </c>
       <c r="D77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>89</v>
@@ -11274,13 +11270,13 @@
         <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>190</v>
+        <v>135</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>240</v>
+        <v>137</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11331,19 +11327,19 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>78</v>
@@ -11352,7 +11348,7 @@
         <v>78</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>78</v>
@@ -11363,20 +11359,18 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="C78" t="s" s="2">
-        <v>486</v>
-      </c>
+      <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G78" t="s" s="2">
         <v>89</v>
@@ -11391,13 +11385,13 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>135</v>
+        <v>210</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>137</v>
+        <v>212</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11448,19 +11442,19 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>78</v>
@@ -11469,7 +11463,7 @@
         <v>78</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>78</v>
+        <v>214</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -11480,10 +11474,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11494,7 +11488,7 @@
         <v>79</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>78</v>
@@ -11506,13 +11500,13 @@
         <v>78</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>212</v>
+        <v>137</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11551,31 +11545,31 @@
         <v>78</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>78</v>
@@ -11584,7 +11578,7 @@
         <v>78</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>214</v>
+        <v>78</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
@@ -11595,10 +11589,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11606,10 +11600,10 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>78</v>
@@ -11621,22 +11615,24 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
-        <v>78</v>
+        <v>482</v>
       </c>
       <c r="S80" t="s" s="2">
         <v>78</v>
@@ -11666,31 +11662,31 @@
         <v>78</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>78</v>
@@ -11699,7 +11695,7 @@
         <v>78</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -11710,10 +11706,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11721,7 +11717,7 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>89</v>
@@ -11736,24 +11732,22 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>103</v>
+        <v>487</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q81" s="2"/>
       <c r="R81" t="s" s="2">
-        <v>486</v>
+        <v>78</v>
       </c>
       <c r="S81" t="s" s="2">
         <v>78</v>
@@ -11795,10 +11789,10 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="AG81" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH81" t="s" s="2">
         <v>89</v>
@@ -11807,7 +11801,7 @@
         <v>78</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>78</v>
@@ -11827,10 +11821,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11838,7 +11832,7 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>89</v>
@@ -11853,22 +11847,24 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>491</v>
+        <v>103</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>78</v>
+        <v>490</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>78</v>
@@ -11910,10 +11906,10 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH82" t="s" s="2">
         <v>89</v>
@@ -11922,7 +11918,7 @@
         <v>78</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>78</v>
@@ -11942,10 +11938,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B83" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11953,10 +11949,10 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>78</v>
@@ -11968,24 +11964,22 @@
         <v>78</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>103</v>
+        <v>493</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q83" s="2"/>
       <c r="R83" t="s" s="2">
-        <v>494</v>
+        <v>78</v>
       </c>
       <c r="S83" t="s" s="2">
         <v>78</v>
@@ -12027,10 +12021,10 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>89</v>
@@ -12039,7 +12033,7 @@
         <v>78</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>78</v>
@@ -12059,12 +12053,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C84" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="B84" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
         <v>78</v>
       </c>
@@ -12073,7 +12069,7 @@
         <v>79</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>78</v>
@@ -12085,13 +12081,13 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>239</v>
+        <v>496</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>240</v>
+        <v>457</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12142,19 +12138,19 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>78</v>
@@ -12163,7 +12159,7 @@
         <v>78</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>78</v>
@@ -12174,14 +12170,12 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="C85" t="s" s="2">
-        <v>499</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
         <v>78</v>
       </c>
@@ -12202,13 +12196,13 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>459</v>
+        <v>210</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>500</v>
+        <v>211</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>461</v>
+        <v>212</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12259,19 +12253,19 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>78</v>
@@ -12280,7 +12274,7 @@
         <v>78</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>78</v>
+        <v>214</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>78</v>
@@ -12291,10 +12285,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12302,10 +12296,10 @@
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>78</v>
@@ -12317,13 +12311,13 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>212</v>
+        <v>137</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12362,31 +12356,31 @@
         <v>78</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>78</v>
@@ -12395,7 +12389,7 @@
         <v>78</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>214</v>
+        <v>78</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>78</v>
@@ -12406,21 +12400,23 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="C87" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="C87" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="D87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>78</v>
@@ -12477,16 +12473,16 @@
         <v>78</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
         <v>219</v>
@@ -12521,20 +12517,18 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B88" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="C88" t="s" s="2">
-        <v>467</v>
-      </c>
+      <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>89</v>
@@ -12549,13 +12543,13 @@
         <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>135</v>
+        <v>210</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>137</v>
+        <v>212</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12606,19 +12600,19 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>78</v>
@@ -12627,7 +12621,7 @@
         <v>78</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>78</v>
+        <v>214</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>78</v>
@@ -12638,10 +12632,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12652,7 +12646,7 @@
         <v>79</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>78</v>
@@ -12664,13 +12658,13 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>212</v>
+        <v>137</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12709,31 +12703,31 @@
         <v>78</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>78</v>
@@ -12742,7 +12736,7 @@
         <v>78</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>214</v>
+        <v>78</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>78</v>
@@ -12753,10 +12747,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12764,10 +12758,10 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>78</v>
@@ -12779,22 +12773,24 @@
         <v>78</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>78</v>
+        <v>463</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>78</v>
@@ -12824,31 +12820,31 @@
         <v>78</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>78</v>
@@ -12857,7 +12853,7 @@
         <v>78</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>78</v>
@@ -12868,10 +12864,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12879,7 +12875,7 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>89</v>
@@ -12894,24 +12890,22 @@
         <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N91" s="2"/>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>467</v>
+        <v>504</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>78</v>
@@ -12929,13 +12923,11 @@
         <v>78</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y91" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y91" s="2"/>
       <c r="Z91" t="s" s="2">
-        <v>78</v>
+        <v>473</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>78</v>
@@ -12953,10 +12945,10 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>89</v>
@@ -12965,7 +12957,7 @@
         <v>78</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>78</v>
@@ -12985,12 +12977,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B92" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="C92" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
         <v>78</v>
       </c>
@@ -13011,13 +13005,13 @@
         <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>239</v>
+        <v>476</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>240</v>
+        <v>137</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13026,7 +13020,7 @@
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>508</v>
+        <v>78</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>78</v>
@@ -13044,11 +13038,13 @@
         <v>78</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y92" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z92" t="s" s="2">
-        <v>477</v>
+        <v>78</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>78</v>
@@ -13066,19 +13062,19 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>78</v>
@@ -13087,7 +13083,7 @@
         <v>78</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>78</v>
@@ -13098,14 +13094,12 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B93" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="C93" t="s" s="2">
-        <v>479</v>
-      </c>
+      <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
         <v>78</v>
       </c>
@@ -13126,13 +13120,13 @@
         <v>78</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>135</v>
+        <v>210</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>480</v>
+        <v>211</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>137</v>
+        <v>212</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13183,19 +13177,19 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>78</v>
@@ -13204,7 +13198,7 @@
         <v>78</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>78</v>
+        <v>214</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>78</v>
@@ -13215,10 +13209,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13229,7 +13223,7 @@
         <v>79</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>78</v>
@@ -13241,13 +13235,13 @@
         <v>78</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>212</v>
+        <v>137</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -13286,31 +13280,31 @@
         <v>78</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AC94" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="AD94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>78</v>
@@ -13319,7 +13313,7 @@
         <v>78</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>214</v>
+        <v>78</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>78</v>
@@ -13330,10 +13324,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13341,10 +13335,10 @@
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>78</v>
@@ -13356,22 +13350,24 @@
         <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q95" s="2"/>
       <c r="R95" t="s" s="2">
-        <v>78</v>
+        <v>475</v>
       </c>
       <c r="S95" t="s" s="2">
         <v>78</v>
@@ -13401,31 +13397,31 @@
         <v>78</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC95" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="AD95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="AG95" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>78</v>
@@ -13434,7 +13430,7 @@
         <v>78</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>78</v>
@@ -13445,10 +13441,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13456,7 +13452,7 @@
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G96" t="s" s="2">
         <v>89</v>
@@ -13471,24 +13467,22 @@
         <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q96" s="2"/>
       <c r="R96" t="s" s="2">
-        <v>479</v>
+        <v>78</v>
       </c>
       <c r="S96" t="s" s="2">
         <v>78</v>
@@ -13530,10 +13524,10 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="AG96" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH96" t="s" s="2">
         <v>89</v>
@@ -13542,7 +13536,7 @@
         <v>78</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>78</v>
@@ -13562,18 +13556,20 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="C97" s="2"/>
+        <v>461</v>
+      </c>
+      <c r="C97" t="s" s="2">
+        <v>482</v>
+      </c>
       <c r="D97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>89</v>
@@ -13588,13 +13584,13 @@
         <v>78</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>190</v>
+        <v>135</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>240</v>
+        <v>137</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13645,19 +13641,19 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>101</v>
+        <v>141</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>78</v>
@@ -13666,7 +13662,7 @@
         <v>78</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>132</v>
+        <v>78</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>78</v>
@@ -13677,20 +13673,18 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B98" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="C98" t="s" s="2">
-        <v>486</v>
-      </c>
+      <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>89</v>
@@ -13705,13 +13699,13 @@
         <v>78</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>135</v>
+        <v>210</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>137</v>
+        <v>212</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13762,19 +13756,19 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>78</v>
@@ -13783,7 +13777,7 @@
         <v>78</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>78</v>
+        <v>214</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>78</v>
@@ -13794,10 +13788,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13808,7 +13802,7 @@
         <v>79</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>78</v>
@@ -13820,13 +13814,13 @@
         <v>78</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>212</v>
+        <v>137</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13865,31 +13859,31 @@
         <v>78</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>78</v>
@@ -13898,7 +13892,7 @@
         <v>78</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>214</v>
+        <v>78</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>78</v>
@@ -13909,10 +13903,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13920,10 +13914,10 @@
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>78</v>
@@ -13935,22 +13929,24 @@
         <v>78</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N100" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>78</v>
+        <v>482</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>78</v>
@@ -13980,31 +13976,31 @@
         <v>78</v>
       </c>
       <c r="AB100" t="s" s="2">
-        <v>138</v>
+        <v>78</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>78</v>
@@ -14013,7 +14009,7 @@
         <v>78</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
@@ -14024,10 +14020,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14035,7 +14031,7 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>89</v>
@@ -14050,24 +14046,22 @@
         <v>78</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>103</v>
+        <v>487</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>486</v>
+        <v>78</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>78</v>
@@ -14109,10 +14103,10 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>89</v>
@@ -14121,7 +14115,7 @@
         <v>78</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>78</v>
@@ -14141,10 +14135,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14152,7 +14146,7 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>89</v>
@@ -14167,22 +14161,24 @@
         <v>78</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>491</v>
+        <v>103</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N102" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q102" s="2"/>
       <c r="R102" t="s" s="2">
-        <v>78</v>
+        <v>490</v>
       </c>
       <c r="S102" t="s" s="2">
         <v>78</v>
@@ -14224,10 +14220,10 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>89</v>
@@ -14236,7 +14232,7 @@
         <v>78</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>78</v>
@@ -14256,10 +14252,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14267,10 +14263,10 @@
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>78</v>
@@ -14282,24 +14278,22 @@
         <v>78</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>103</v>
+        <v>493</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>234</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q103" s="2"/>
       <c r="R103" t="s" s="2">
-        <v>494</v>
+        <v>78</v>
       </c>
       <c r="S103" t="s" s="2">
         <v>78</v>
@@ -14341,10 +14335,10 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH103" t="s" s="2">
         <v>89</v>
@@ -14353,7 +14347,7 @@
         <v>78</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>78</v>
@@ -14373,10 +14367,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>496</v>
+        <v>517</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14387,7 +14381,7 @@
         <v>79</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>78</v>
@@ -14396,18 +14390,20 @@
         <v>78</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>497</v>
+        <v>210</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>239</v>
+        <v>518</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N104" s="2"/>
+        <v>519</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>520</v>
+      </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>78</v>
@@ -14456,7 +14452,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>243</v>
+        <v>521</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -14465,7 +14461,7 @@
         <v>89</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>78</v>
+        <v>522</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>101</v>
@@ -14488,10 +14484,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14514,16 +14510,16 @@
         <v>90</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>210</v>
+        <v>103</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14549,13 +14545,13 @@
         <v>78</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>78</v>
+        <v>438</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>78</v>
+        <v>527</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>78</v>
+        <v>528</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>78</v>
@@ -14573,7 +14569,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -14582,7 +14578,7 @@
         <v>89</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>526</v>
+        <v>78</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>101</v>
@@ -14605,10 +14601,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14631,16 +14627,16 @@
         <v>90</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14666,13 +14662,13 @@
         <v>78</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>442</v>
+        <v>78</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>531</v>
+        <v>78</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>532</v>
+        <v>78</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>78</v>
@@ -14690,7 +14686,7 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -14711,7 +14707,7 @@
         <v>78</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>132</v>
+        <v>535</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>78</v>
@@ -14722,10 +14718,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14748,16 +14744,16 @@
         <v>90</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14807,7 +14803,7 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -14828,7 +14824,7 @@
         <v>78</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>539</v>
+        <v>132</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>78</v>
@@ -14839,10 +14835,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14856,7 +14852,7 @@
         <v>89</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>78</v>
@@ -14865,17 +14861,15 @@
         <v>90</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>210</v>
+        <v>542</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>543</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>78</v>
@@ -14924,13 +14918,13 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI108" t="s" s="2">
         <v>78</v>
@@ -14939,13 +14933,13 @@
         <v>101</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>78</v>
+        <v>545</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>78</v>
+        <v>546</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>132</v>
+        <v>547</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>78</v>
@@ -14956,10 +14950,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14970,25 +14964,25 @@
         <v>79</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J109" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>546</v>
+        <v>190</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15015,13 +15009,13 @@
         <v>78</v>
       </c>
       <c r="X109" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>78</v>
+        <v>551</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>78</v>
+        <v>552</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>78</v>
@@ -15039,7 +15033,7 @@
         <v>78</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>79</v>
@@ -15054,13 +15048,13 @@
         <v>101</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>550</v>
+        <v>78</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>78</v>
@@ -15071,10 +15065,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15088,7 +15082,7 @@
         <v>80</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>78</v>
@@ -15097,13 +15091,13 @@
         <v>78</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>190</v>
+        <v>556</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -15130,31 +15124,31 @@
         <v>78</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="Y110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF110" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="Z110" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>552</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>79</v>
@@ -15169,13 +15163,13 @@
         <v>101</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="AL110" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>558</v>
+        <v>132</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>78</v>
@@ -15186,10 +15180,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15200,19 +15194,19 @@
         <v>79</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I111" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I111" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J111" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>560</v>
+        <v>296</v>
       </c>
       <c r="L111" t="s" s="2">
         <v>561</v>
@@ -15220,12 +15214,16 @@
       <c r="M111" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="N111" s="2"/>
+      <c r="N111" t="s" s="2">
+        <v>563</v>
+      </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q111" s="2"/>
+      <c r="Q111" t="s" s="2">
+        <v>564</v>
+      </c>
       <c r="R111" t="s" s="2">
         <v>78</v>
       </c>
@@ -15269,13 +15267,13 @@
         <v>78</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>78</v>
@@ -15284,10 +15282,10 @@
         <v>101</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>563</v>
+        <v>78</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>78</v>
+        <v>565</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>132</v>
@@ -15301,10 +15299,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15315,36 +15313,32 @@
         <v>79</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>300</v>
+        <v>190</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>567</v>
-      </c>
+        <v>568</v>
+      </c>
+      <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q112" t="s" s="2">
-        <v>568</v>
-      </c>
+      <c r="Q112" s="2"/>
       <c r="R112" t="s" s="2">
         <v>78</v>
       </c>
@@ -15364,13 +15358,13 @@
         <v>78</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>78</v>
+        <v>569</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>78</v>
+        <v>570</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>78</v>
@@ -15388,13 +15382,13 @@
         <v>78</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>78</v>
@@ -15406,7 +15400,7 @@
         <v>78</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>569</v>
+        <v>78</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>132</v>
@@ -15420,10 +15414,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15446,13 +15440,13 @@
         <v>78</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>190</v>
+        <v>422</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -15479,13 +15473,13 @@
         <v>78</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>573</v>
+        <v>78</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>574</v>
+        <v>78</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>78</v>
@@ -15503,7 +15497,7 @@
         <v>78</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>79</v>
@@ -15515,7 +15509,7 @@
         <v>78</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>101</v>
+        <v>574</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>78</v>
@@ -15549,7 +15543,7 @@
         <v>79</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>78</v>
@@ -15561,13 +15555,13 @@
         <v>78</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>426</v>
+        <v>210</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>576</v>
+        <v>211</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>577</v>
+        <v>212</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15618,19 +15612,19 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>575</v>
+        <v>213</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>578</v>
+        <v>78</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>78</v>
@@ -15639,7 +15633,7 @@
         <v>78</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>132</v>
+        <v>214</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>78</v>
@@ -15650,21 +15644,21 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>78</v>
+        <v>164</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>78</v>
@@ -15676,15 +15670,17 @@
         <v>78</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N115" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>78</v>
@@ -15733,19 +15729,19 @@
         <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>78</v>
@@ -15765,14 +15761,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>164</v>
+        <v>431</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -15785,24 +15781,26 @@
         <v>78</v>
       </c>
       <c r="I116" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K116" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>216</v>
+        <v>432</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>217</v>
+        <v>433</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="O116" s="2"/>
+      <c r="O116" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>78</v>
       </c>
@@ -15850,7 +15848,7 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>219</v>
+        <v>434</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -15871,7 +15869,7 @@
         <v>78</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>214</v>
+        <v>132</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>78</v>
@@ -15882,46 +15880,42 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>435</v>
+        <v>78</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>135</v>
+        <v>210</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>436</v>
+        <v>579</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>78</v>
       </c>
@@ -15969,25 +15963,25 @@
         <v>78</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>438</v>
+        <v>578</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="AK117" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>78</v>
+        <v>581</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>132</v>
@@ -16027,7 +16021,7 @@
         <v>78</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>210</v>
+        <v>103</v>
       </c>
       <c r="L118" t="s" s="2">
         <v>583</v>
@@ -16102,7 +16096,7 @@
         <v>78</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>585</v>
+        <v>78</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>132</v>
@@ -16116,10 +16110,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16142,13 +16136,13 @@
         <v>78</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>103</v>
+        <v>332</v>
       </c>
       <c r="L119" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M119" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -16199,7 +16193,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16217,7 +16211,7 @@
         <v>78</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>78</v>
+        <v>588</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>132</v>
@@ -16257,7 +16251,7 @@
         <v>78</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="L120" t="s" s="2">
         <v>590</v>
@@ -16360,7 +16354,7 @@
         <v>79</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>78</v>
@@ -16372,7 +16366,7 @@
         <v>78</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>336</v>
+        <v>190</v>
       </c>
       <c r="L121" t="s" s="2">
         <v>594</v>
@@ -16405,13 +16399,13 @@
         <v>78</v>
       </c>
       <c r="X121" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="Y121" t="s" s="2">
-        <v>78</v>
+        <v>596</v>
       </c>
       <c r="Z121" t="s" s="2">
-        <v>78</v>
+        <v>597</v>
       </c>
       <c r="AA121" t="s" s="2">
         <v>78</v>
@@ -16435,7 +16429,7 @@
         <v>79</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>78</v>
@@ -16447,7 +16441,7 @@
         <v>78</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>132</v>
@@ -16461,10 +16455,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16475,7 +16469,7 @@
         <v>79</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>78</v>
@@ -16490,10 +16484,10 @@
         <v>190</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -16523,10 +16517,10 @@
         <v>194</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>78</v>
@@ -16544,13 +16538,13 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>78</v>
@@ -16562,7 +16556,7 @@
         <v>78</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>602</v>
+        <v>78</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>132</v>
@@ -16576,10 +16570,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16590,7 +16584,7 @@
         <v>79</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>78</v>
@@ -16602,15 +16596,17 @@
         <v>78</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>190</v>
+        <v>422</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="N123" s="2"/>
+        <v>606</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>607</v>
+      </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>78</v>
@@ -16635,13 +16631,13 @@
         <v>78</v>
       </c>
       <c r="X123" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="Y123" t="s" s="2">
-        <v>606</v>
+        <v>78</v>
       </c>
       <c r="Z123" t="s" s="2">
-        <v>607</v>
+        <v>78</v>
       </c>
       <c r="AA123" t="s" s="2">
         <v>78</v>
@@ -16659,13 +16655,13 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>78</v>
@@ -16677,10 +16673,10 @@
         <v>78</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>78</v>
+        <v>608</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>132</v>
+        <v>609</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>78</v>
@@ -16691,10 +16687,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16705,7 +16701,7 @@
         <v>79</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>78</v>
@@ -16717,17 +16713,15 @@
         <v>78</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>426</v>
+        <v>210</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>609</v>
+        <v>211</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>611</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N124" s="2"/>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>78</v>
@@ -16776,28 +16770,28 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>608</v>
+        <v>213</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK124" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>612</v>
+        <v>78</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>613</v>
+        <v>214</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>78</v>
@@ -16808,21 +16802,21 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>78</v>
+        <v>164</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>78</v>
@@ -16834,15 +16828,17 @@
         <v>78</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N125" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>78</v>
@@ -16891,19 +16887,19 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>78</v>
@@ -16923,14 +16919,14 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>164</v>
+        <v>431</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -16943,24 +16939,26 @@
         <v>78</v>
       </c>
       <c r="I126" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K126" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>216</v>
+        <v>432</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>217</v>
+        <v>433</v>
       </c>
       <c r="N126" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="O126" s="2"/>
+      <c r="O126" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="P126" t="s" s="2">
         <v>78</v>
       </c>
@@ -17008,7 +17006,7 @@
         <v>78</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>219</v>
+        <v>434</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>79</v>
@@ -17029,7 +17027,7 @@
         <v>78</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>214</v>
+        <v>132</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>78</v>
@@ -17040,46 +17038,42 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>435</v>
+        <v>78</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I127" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>135</v>
+        <v>332</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>436</v>
+        <v>614</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>615</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>78</v>
       </c>
@@ -17127,28 +17121,28 @@
         <v>78</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>438</v>
+        <v>613</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>78</v>
+        <v>616</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>132</v>
+        <v>338</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>78</v>
@@ -17185,13 +17179,13 @@
         <v>78</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>336</v>
+        <v>618</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -17260,10 +17254,10 @@
         <v>78</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>342</v>
+        <v>622</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>78</v>
@@ -17274,10 +17268,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17300,13 +17294,13 @@
         <v>78</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>622</v>
+        <v>296</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -17357,7 +17351,7 @@
         <v>78</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>79</v>
@@ -17375,10 +17369,10 @@
         <v>78</v>
       </c>
       <c r="AL129" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>78</v>
@@ -17389,10 +17383,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17403,10 +17397,10 @@
         <v>79</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H130" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I130" t="s" s="2">
         <v>78</v>
@@ -17415,13 +17409,13 @@
         <v>78</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>300</v>
+        <v>422</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -17472,13 +17466,13 @@
         <v>78</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>78</v>
@@ -17490,10 +17484,10 @@
         <v>78</v>
       </c>
       <c r="AL130" t="s" s="2">
-        <v>630</v>
+        <v>78</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>631</v>
+        <v>132</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>78</v>
@@ -17504,10 +17498,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17518,10 +17512,10 @@
         <v>79</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H131" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I131" t="s" s="2">
         <v>78</v>
@@ -17530,13 +17524,13 @@
         <v>78</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>426</v>
+        <v>210</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>633</v>
+        <v>211</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>634</v>
+        <v>212</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -17587,19 +17581,19 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>632</v>
+        <v>213</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>78</v>
@@ -17608,7 +17602,7 @@
         <v>78</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>132</v>
+        <v>214</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>78</v>
@@ -17619,21 +17613,21 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>78</v>
+        <v>164</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>78</v>
@@ -17645,15 +17639,17 @@
         <v>78</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>210</v>
+        <v>135</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N132" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>78</v>
@@ -17702,19 +17698,19 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="AK132" t="s" s="2">
         <v>78</v>
@@ -17734,14 +17730,14 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>164</v>
+        <v>431</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -17754,24 +17750,26 @@
         <v>78</v>
       </c>
       <c r="I133" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K133" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>216</v>
+        <v>432</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>217</v>
+        <v>433</v>
       </c>
       <c r="N133" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="O133" s="2"/>
+      <c r="O133" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="P133" t="s" s="2">
         <v>78</v>
       </c>
@@ -17819,7 +17817,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>219</v>
+        <v>434</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -17840,7 +17838,7 @@
         <v>78</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>214</v>
+        <v>132</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>78</v>
@@ -17851,46 +17849,42 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
-        <v>435</v>
+        <v>78</v>
       </c>
       <c r="E134" s="2"/>
       <c r="F134" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I134" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>135</v>
+        <v>210</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>436</v>
+        <v>635</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="O134" t="s" s="2">
-        <v>168</v>
-      </c>
+        <v>636</v>
+      </c>
+      <c r="N134" s="2"/>
+      <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>78</v>
       </c>
@@ -17938,19 +17932,19 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>438</v>
+        <v>634</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>78</v>
@@ -17970,10 +17964,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17996,13 +17990,13 @@
         <v>78</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>210</v>
+        <v>383</v>
       </c>
       <c r="L135" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="M135" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -18053,7 +18047,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18085,10 +18079,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18099,7 +18093,7 @@
         <v>79</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>78</v>
@@ -18111,13 +18105,13 @@
         <v>78</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>387</v>
+        <v>190</v>
       </c>
       <c r="L136" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="M136" t="s" s="2">
         <v>642</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>643</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -18144,13 +18138,13 @@
         <v>78</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>78</v>
+        <v>194</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>78</v>
+        <v>643</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>78</v>
+        <v>644</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>78</v>
@@ -18168,13 +18162,13 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>78</v>
@@ -18200,10 +18194,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -18211,10 +18205,10 @@
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>78</v>
@@ -18226,15 +18220,17 @@
         <v>78</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>190</v>
+        <v>646</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="N137" s="2"/>
+        <v>648</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>649</v>
+      </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>78</v>
@@ -18259,37 +18255,35 @@
         <v>78</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>194</v>
+        <v>78</v>
       </c>
       <c r="Y137" t="s" s="2">
-        <v>647</v>
+        <v>78</v>
       </c>
       <c r="Z137" t="s" s="2">
-        <v>648</v>
+        <v>78</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB137" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC137" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>650</v>
+      </c>
+      <c r="AC137" s="2"/>
       <c r="AD137" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE137" t="s" s="2">
-        <v>78</v>
+        <v>651</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AG137" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>78</v>
@@ -18315,12 +18309,14 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="C138" s="2"/>
+        <v>645</v>
+      </c>
+      <c r="C138" t="s" s="2">
+        <v>653</v>
+      </c>
       <c r="D138" t="s" s="2">
         <v>78</v>
       </c>
@@ -18341,16 +18337,16 @@
         <v>78</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -18388,17 +18384,19 @@
         <v>78</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="AC138" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC138" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD138" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>242</v>
+        <v>78</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>89</v>
@@ -18430,20 +18428,18 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="C139" t="s" s="2">
         <v>655</v>
       </c>
+      <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G139" t="s" s="2">
         <v>89</v>
@@ -18458,16 +18454,16 @@
         <v>78</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -18517,10 +18513,10 @@
         <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="AG139" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH139" t="s" s="2">
         <v>89</v>
@@ -18547,125 +18543,8 @@
         <v>78</v>
       </c>
     </row>
-    <row r="140" hidden="true">
-      <c r="A140" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="B140" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="C140" s="2"/>
-      <c r="D140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E140" s="2"/>
-      <c r="F140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="G140" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K140" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="L140" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="O140" s="2"/>
-      <c r="P140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q140" s="2"/>
-      <c r="R140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF140" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="AG140" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH140" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ140" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM140" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AN140" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO140" t="s" s="2">
-        <v>78</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AO140">
+  <autoFilter ref="A1:AO139">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -18675,7 +18554,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI139">
+  <conditionalFormatting sqref="A2:AI138">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
